--- a/Packages/cn.etetet.numeric/Luban/Config/Datas/NumericType.xlsx
+++ b/Packages/cn.etetet.numeric/Luban/Config/Datas/NumericType.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Config/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05ET\MatchTest\ETGame\Packages\cn.etetet.numeric\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD64FDAB-A42C-0E45-A88C-3D366BCC2C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8F8CF6-532A-4872-A6EB-E44D2ACDD709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="2740" windowWidth="32880" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="7770" windowWidth="28830" windowHeight="7830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NumericType" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -34,6 +34,9 @@
     <t>NeedSaveDB</t>
   </si>
   <si>
+    <t>NoticeType</t>
+  </si>
+  <si>
     <t>MaxNumericType</t>
   </si>
   <si>
@@ -80,25 +83,31 @@
   </si>
   <si>
     <t>影响的属性id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoNotice = 0,
+Self = 1,
+Broadcast = 2,
+BroadcastWithoutSelf = 3,</t>
   </si>
   <si>
     <r>
       <rPr>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+        <family val="2"/>
+        <color theme="1"/>
         <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
       </rPr>
       <t>填对应的最大值Numeric</t>
     </r>
     <r>
       <rPr>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+        <family val="2"/>
+        <color theme="1"/>
         <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Id</t>
     </r>
@@ -110,6 +119,9 @@
     <t>Speed</t>
   </si>
   <si>
+    <t>Broadcast</t>
+  </si>
+  <si>
     <t>HP</t>
   </si>
   <si>
@@ -128,6 +140,9 @@
     <t>AOI</t>
   </si>
   <si>
+    <t>Self</t>
+  </si>
+  <si>
     <t>Height</t>
   </si>
   <si>
@@ -137,22 +152,7 @@
     <t>AI</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>出生X坐标</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>出生Y坐标</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>出生Z坐标</t>
+    <t>NoNotice</t>
   </si>
   <si>
     <t>Stun</t>
@@ -161,47 +161,18 @@
     <t>眩晕</t>
   </si>
   <si>
-    <t>出生朝向</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yaw</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Phase</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>相位</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>NoticeType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>NoNotice = 0,
-Self = 1,
-Broadcast = 2,
-BroadcastWithoutSelf = 3,</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>NoNotice</t>
-  </si>
-  <si>
-    <t>Broadcast</t>
-  </si>
-  <si>
-    <t>Self</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,13 +210,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -272,21 +236,21 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -563,22 +527,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
+    <col min="3" max="3" width="29.625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="31.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.875" customWidth="1"/>
+    <col min="9" max="9" width="31.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" ht="15.75">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -593,89 +557,89 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="17">
-      <c r="A2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="2" ht="15.75">
+      <c r="A2" s="0" t="s">
+        <v>7</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75">
+      <c r="A3" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>12</v>
+    <row r="4" ht="15.75">
+      <c r="A4" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="57">
+      <c r="A5" s="0" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="60">
-      <c r="A5" t="s">
-        <v>12</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -683,21 +647,21 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="B6" s="4">
         <v>1000</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -707,17 +671,17 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7">
       <c r="B7" s="4">
         <v>1001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4">
@@ -727,19 +691,19 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H7" s="4">
         <v>1002</v>
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8">
       <c r="B8" s="4">
         <v>1002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4">
@@ -749,17 +713,17 @@
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9">
       <c r="B9" s="4">
         <v>1003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4">
@@ -769,19 +733,19 @@
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H9" s="4">
         <v>1004</v>
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10">
       <c r="B10" s="4">
         <v>1004</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4">
@@ -791,17 +755,17 @@
         <v>1</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11">
       <c r="B11" s="4">
         <v>1005</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4">
@@ -811,17 +775,17 @@
         <v>1</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12">
       <c r="B12" s="4">
         <v>1006</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4">
@@ -831,17 +795,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13">
       <c r="B13" s="4">
         <v>1007</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4">
@@ -851,17 +815,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14">
       <c r="B14" s="4">
         <v>1008</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4">
@@ -871,17 +835,17 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15">
       <c r="B15" s="4">
         <v>1009</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4">
@@ -891,144 +855,62 @@
         <v>1</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16">
       <c r="B16" s="4">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17">
       <c r="B17" s="4">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
       </c>
       <c r="F17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="4">
-        <v>1012</v>
-      </c>
-      <c r="C18" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="4">
-        <v>1013</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="4">
-        <v>1014</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="4">
-        <v>1015</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4">
-        <v>1</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.numeric/Luban/Config/Datas/NumericType.xlsx
+++ b/Packages/cn.etetet.numeric/Luban/Config/Datas/NumericType.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>相位</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>攻击力</t>
   </si>
 </sst>
 </file>
@@ -527,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -902,6 +908,23 @@
         <v>36</v>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" s="0">
+        <v>1010</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="0">
+        <v>1</v>
+      </c>
+      <c r="F18" s="0">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
